--- a/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
+++ b/data/input/Excel_files/Soorten_bwk_afstanden.xlsx
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>189</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>44</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>44</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>44</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>44</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>1000</v>
       </c>
       <c r="G67" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H67" t="s">
         <v>288</v>
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>189</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>44</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>44</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>44</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>189</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>44</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>44</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>44</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>44</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>44</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>44</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>100</v>
       </c>
       <c r="G134" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H134" t="s">
         <v>288</v>
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>44</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>44</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>189</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>44</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -8250,12 +8250,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>44</v>
       </c>
       <c r="B159" t="s">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="C159" t="s">
         <v>262</v>
@@ -8276,7 +8276,7 @@
         <v>289</v>
       </c>
       <c r="J159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -8294,30 +8294,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="C160" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D160">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="E160">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F160">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="G160" t="s">
         <v>308</v>
       </c>
       <c r="H160" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -8326,13 +8326,13 @@
         <v>0</v>
       </c>
       <c r="L160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O160">
         <v>0</v>
@@ -8390,21 +8390,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C163" t="s">
         <v>269</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E163">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F163">
         <v>10000</v>
@@ -8434,56 +8434,56 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B164" t="s">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="C164" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D164">
-        <v>25</v>
+        <v>0.16</v>
       </c>
       <c r="E164">
+        <v>20</v>
+      </c>
+      <c r="F164">
         <v>100</v>
-      </c>
-      <c r="F164">
-        <v>10000</v>
       </c>
       <c r="G164" t="s">
         <v>308</v>
       </c>
       <c r="H164" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J164">
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164">
         <v>0</v>
       </c>
       <c r="M164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>44</v>
       </c>
       <c r="B165" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C165" t="s">
         <v>262</v>
@@ -8513,7 +8513,7 @@
         <v>0</v>
       </c>
       <c r="M165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N165">
         <v>1</v>
@@ -8569,12 +8569,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>44</v>
       </c>
       <c r="B167" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C167" t="s">
         <v>262</v>
@@ -8595,16 +8595,16 @@
         <v>289</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167">
         <v>1</v>
       </c>
       <c r="L167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N167">
         <v>1</v>
@@ -8613,12 +8613,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>44</v>
       </c>
       <c r="B168" t="s">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="C168" t="s">
         <v>262</v>
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="K168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168">
         <v>1</v>
@@ -8654,7 +8654,7 @@
         <v>1</v>
       </c>
       <c r="O168">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
@@ -8798,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>44</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>44</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>44</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>44</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>44</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>189</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>44</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>44</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>44</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>44</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>44</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -10139,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -10159,7 +10159,7 @@
         <v>100</v>
       </c>
       <c r="G202" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H202" t="s">
         <v>288</v>
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>44</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>44</v>
       </c>
@@ -10271,7 +10271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>44</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>44</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>189</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>44</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>189</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>44</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>189</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>44</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>44</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>44</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>44</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>189</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>44</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>44</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>44</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>44</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>44</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>44</v>
       </c>
@@ -13153,7 +13153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>44</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>44</v>
       </c>
@@ -13746,7 +13746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>189</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>44</v>
       </c>
@@ -14080,7 +14080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>44</v>
       </c>
@@ -14165,7 +14165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>44</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>44</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>44</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>44</v>
       </c>
@@ -15224,7 +15224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>44</v>
       </c>
@@ -15268,7 +15268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>44</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>189</v>
       </c>
@@ -15359,7 +15359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>44</v>
       </c>
@@ -15520,7 +15520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>44</v>
       </c>
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>44</v>
       </c>
@@ -15652,7 +15652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>44</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>189</v>
       </c>
@@ -15884,7 +15884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>44</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>44</v>
       </c>
@@ -16019,7 +16019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>44</v>
       </c>
@@ -16063,7 +16063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>44</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>44</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>25</v>
       </c>
@@ -16591,7 +16591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>25</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>25</v>
       </c>
@@ -16673,7 +16673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>189</v>
       </c>
@@ -16720,7 +16720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>189</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>189</v>
       </c>
@@ -16954,15 +16954,18 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O357">
-    <filterColumn colId="1">
+    <filterColumn colId="5">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="6">
       <filters>
-        <filter val="zwarteheidelibel"/>
-        <filter val="zwartespecht"/>
-        <filter val="zwartestern"/>
+        <filter val="Simpel"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:O358">
-      <sortCondition ref="B1:B358"/>
+    <sortState ref="A3:O344">
+      <sortCondition ref="B1:B357"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
